--- a/AI_Project_Ideas_Scorecard.xlsx
+++ b/AI_Project_Ideas_Scorecard.xlsx
@@ -11,7 +11,7 @@
     <sheet name="AI Project Ideas Scorecard" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'AI Project Ideas Scorecard'!$A$1:$M$26</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'AI Project Ideas Scorecard'!$A$1:$M$37</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="108">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -78,6 +78,66 @@
 (with PI)</t>
   </si>
   <si>
+    <t xml:space="preserve">Accent/Voice AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accent-Fair Voice AI ★</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine-tunes Whisper for South Asian English accents, released as open API/extension. Fixes 40%+ higher error rates for non-native speakers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deepfake Voice Firewall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real-time call authentication analyzing behavioral speech patterns (vocabulary, pauses, micro-expressions) to detect AI-cloned voices during calls.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financial Planning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Financial Life-Event Replanner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detects life events from financial data (new job, move, freelancing) and auto-triggers personalized financial replans with quarterly tax optimization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Phishing Simulation &amp; Training Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generates hyper-realistic phishing attacks tailored to each employee's role and behavior, then provides personalized security training based on who fell for what.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metacognitive Learning Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI that teaches students HOW to learn by analyzing their patterns, identifying strategies, and tracking long-term retention instead of just test scores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fitness/Wellness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Gym Form Coach (Phone Camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real-time exercise form correction using just a phone camera with sub-100ms feedback, personal biomechanics profiling, and injury prediction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real-Time Transaction Anomaly Mesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decentralized fraud detection where multiple small businesses share anonymized fraud patterns, creating collective intelligence without exposing individual data.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Environment</t>
   </si>
   <si>
@@ -96,6 +156,24 @@
     <t xml:space="preserve">Analyzes individual longitudinal data (sleep, social, location) to identify which specific life factors trigger mental health episodes for each person.</t>
   </si>
   <si>
+    <t xml:space="preserve">Content Creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-Production Content Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predicts video/content performance BEFORE production using channel history, trends, and audience data so creators don't waste hours on flops.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply Chain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Supplier Risk &amp; Disruption Predictor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitors news, weather, geopolitics, and shipping data to predict supply chain disruptions 2-4 weeks ahead and recommend alternative suppliers automatically.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Civic Tech</t>
   </si>
   <si>
@@ -105,15 +183,6 @@
     <t xml:space="preserve">Real-time AI mapping block-level disparities (health, environment, economy) designed for residents to ask questions and get data-driven answers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metacognitive Learning Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI that teaches students HOW to learn by analyzing their patterns, identifying strategies, and tracking long-term retention instead of just test scores.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Accessibility</t>
   </si>
   <si>
@@ -123,24 +192,6 @@
     <t xml:space="preserve">Combines vision, NLP, and haptic feedback to enable real-time nuanced conversation for deaf-blind users through wearable devices.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deepfake Voice Firewall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real-time call authentication analyzing behavioral speech patterns (vocabulary, pauses, micro-expressions) to detect AI-cloned voices during calls.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content Creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-Production Content Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predicts video/content performance BEFORE production using channel history, trends, and audience data so creators don't waste hours on flops.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Predictive Maint.</t>
   </si>
   <si>
@@ -150,58 +201,73 @@
     <t xml:space="preserve">Predicts failures in personal electronics/appliances before they happen, with warranty-aware alerts and repair-vs-replace economics.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fitness/Wellness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Gym Form Coach (Phone Camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real-time exercise form correction using just a phone camera with sub-100ms feedback, personal biomechanics profiling, and injury prediction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accent/Voice AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accent-Fair Voice AI ★</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fine-tunes Whisper for South Asian English accents, released as open API/extension. Fixes 40%+ higher error rates for non-native speakers.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cross-Game Cheat Intelligence Network</t>
   </si>
   <si>
     <t xml:space="preserve">Shared cheat detection platform for indie studios — detects cheat patterns in one game and alerts all connected studios before cheaters migrate.</t>
   </si>
   <si>
-    <t xml:space="preserve">Supply Chain</t>
-  </si>
-  <si>
     <t xml:space="preserve">Phantom Inventory Killer (SME Data Cleaner)</t>
   </si>
   <si>
     <t xml:space="preserve">AI data preparation layer for SMEs that unifies messy inventory data and provides cash-flow-aware demand forecasting for small businesses.</t>
   </si>
   <si>
+    <t xml:space="preserve">Art/Music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live Jam AI — Real-Time Musical Co-Improvisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI instrument that listens to you play and generates complementary harmonies/bass lines in &lt;50ms, learning your style over sessions. Ships as VST plugin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Sleep-to-Performance Optimizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correlates sleep architecture with next-day cognitive/physical performance, prescribing personalized micro-interventions and optimal sleep timing for tomorrow's tasks.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gaming</t>
   </si>
   <si>
+    <t xml:space="preserve">AI Multiplayer Balance Testing Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud platform running headless AI agents against multiplayer servers to detect balance issues, economy exploits, and cross-class viability at scale for indie devs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethical Dynamic Pricing for SMB Retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transparency-first AI pricing for small retailers that adjusts prices based on inventory, demand, and competitor data — consumer-friendly, not predatory.</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI Dungeon Master — NPC Behavior Engine</t>
   </si>
   <si>
     <t xml:space="preserve">No-code behavioral AI engine where indie devs describe NPC personalities in natural language and get emergent RL-driven behavior in-game.</t>
   </si>
   <si>
-    <t xml:space="preserve">Art/Music</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live Jam AI — Real-Time Musical Co-Improvisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI instrument that listens to you play and generates complementary harmonies/bass lines in &lt;50ms, learning your style over sessions. Ships as VST plugin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retail</t>
+    <t xml:space="preserve">AI Warranty Fraud &amp; Claim Optimizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dual-use: helps consumers maximize legitimate warranty claims before expiry, and helps manufacturers detect fraudulent claims using pattern analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Emotion-Responsive Visual + Music Generator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyzes audience reactions (facial expressions, biometrics) and dynamically generates responsive visuals and music for live events, installations, or therapy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Content ROI Attribution Engine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracks how individual videos/posts drive specific monetization outcomes (Patreon, sponsors, affiliates) to tell creators which content type is truly worth making.</t>
   </si>
   <si>
     <t xml:space="preserve">Retail Shelf Psychologist — Customer Intent Prediction</t>
@@ -210,70 +276,91 @@
     <t xml:space="preserve">Uses existing store cameras to predict purchase abandonment and alert staff in real-time, plus optimize store layout based on engagement data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Financial Planning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Financial Life-Event Replanner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detects life events from financial data (new job, move, freelancing) and auto-triggers personalized financial replans with quarterly tax optimization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Phishing Simulation &amp; Training Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generates hyper-realistic phishing attacks tailored to each employee's role and behavior, then provides personalized security training based on who fell for what.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Sleep-to-Performance Optimizer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correlates sleep architecture with next-day cognitive/physical performance, prescribing personalized micro-interventions and optimal sleep timing for tomorrow's tasks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud Detection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real-Time Transaction Anomaly Mesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decentralized fraud detection where multiple small businesses share anonymized fraud patterns, creating collective intelligence without exposing individual data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Supplier Risk &amp; Disruption Predictor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitors news, weather, geopolitics, and shipping data to predict supply chain disruptions 2-4 weeks ahead and recommend alternative suppliers automatically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Content ROI Attribution Engine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracks how individual videos/posts drive specific monetization outcomes (Patreon, sponsors, affiliates) to tell creators which content type is truly worth making.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Multiplayer Balance Testing Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud platform running headless AI agents against multiplayer servers to detect balance issues, economy exploits, and cross-class viability at scale for indie devs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethical Dynamic Pricing for SMB Retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transparency-first AI pricing for small retailers that adjusts prices based on inventory, demand, and competitor data — consumer-friendly, not predatory.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Warranty Fraud &amp; Claim Optimizer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual-use: helps consumers maximize legitimate warranty claims before expiry, and helps manufacturers detect fraudulent claims using pattern analysis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Emotion-Responsive Visual + Music Generator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyzes audience reactions (facial expressions, biometrics) and dynamically generates responsive visuals and music for live events, installations, or therapy.</t>
+    <t xml:space="preserve">JOB LISTING-INSPIRED IDEAS (sourced from LinkedIn, Etsy, PayPal, Netic, Anthropic &amp; industry research)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search/Rec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-Powered Semantic Search Engine for E-Commerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build a search system using LLM embeddings (Llama/Qwen) for product discovery. Handles vague queries like 'something cozy for winter' using vector similarity + re-ranking. Directly mirrors Etsy/Amazon ML engineer roles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real-Time Transaction Fraud Detector with Continuous Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anomaly detection system for payment transactions using supervised + unsupervised learning that adapts to new fraud patterns via continual learning. Mirrors PayPal's exact ML engineer job requirements (anomaly detection, identity models, real-time systems).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLP/LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open-Source LLM Fine-Tuning &amp; Evaluation Toolkit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End-to-end toolkit for fine-tuning open-source LLMs (Llama, Mistral) on custom datasets with built-in eval benchmarks. Every AI company (Etsy, Netic, Anthropic) lists LLM fine-tuning as a core requirement. High portfolio value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production ML Pipeline Monitor &amp; Auto-Retrainer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System that monitors deployed ML models for drift, performance degradation, and data quality issues — then auto-triggers retraining. Every job listing mentions 'deploying and monitoring production ML systems' as critical.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Visual Quality Inspector for Manufacturing/Retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer vision system that detects product defects, counterfeit items, or quality issues from images. Uses transfer learning on pre-trained models. Addresses CV skills listed in 60%+ of AI engineer roles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-Powered Phishing Email Detector &amp; Classifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLP model that classifies emails as phishing/legitimate using transformer models, with explainable AI showing why. Combines NLP + cybersecurity — two of the hottest hiring domains. Deployable as API or browser extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommendation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personalized Content Recommendation Engine with A/B Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-stack recommendation system using collaborative filtering + content-based approaches with built-in A/B experimentation framework. Etsy, Netflix, Spotify all hire for this exact skill. Shows end-to-end ML product thinking.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated Data Quality &amp; Feature Engineering Pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tool that ingests raw messy data, auto-detects quality issues (missing values, outliers, type mismatches), generates features, and outputs clean ML-ready datasets. Every ML job requires 'data pipeline' and 'feature engineering' skills.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinforcement Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Game Agent Using Deep Reinforcement Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train an RL agent to play a custom game environment using DQN/PPO algorithms. PayPal lists 'reinforcement learning and contextual bandits' as preferred. Demonstrates cutting-edge ML skills that most candidates lack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-Stack AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-Powered Customer Support Chatbot with RAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production-ready chatbot using Retrieval Augmented Generation — connects to a knowledge base, retrieves relevant docs, and generates accurate answers. Demonstrates REST API development, NLP, LLMs, and cloud deployment — all top-listed job requirements.</t>
   </si>
 </sst>
 </file>
@@ -336,7 +423,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,14 +438,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFBF8F00"/>
+        <bgColor rgb="FF808000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -411,7 +516,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -460,6 +565,50 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,11 +618,19 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1F4E79"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBF8F00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -489,6 +646,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -497,6 +670,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -522,8 +703,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -539,7 +720,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -548,7 +729,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFBF8F00"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
@@ -749,8 +930,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M37"/>
+  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
@@ -803,7 +984,7 @@
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>13</v>
@@ -815,81 +996,81 @@
         <v>15</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="L2" s="6" t="n">
         <f aca="false">SUM(E2:J2)</f>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M2" s="6" t="n">
         <f aca="false">SUM(E2:K2)</f>
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="L3" s="11" t="n">
+      <c r="E3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L3" s="6" t="n">
         <f aca="false">SUM(E3:J3)</f>
-        <v>44</v>
-      </c>
-      <c r="M3" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="M3" s="6" t="n">
         <f aca="false">SUM(E3:K3)</f>
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>19</v>
@@ -901,231 +1082,231 @@
         <v>21</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>8</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L4" s="6" t="n">
         <f aca="false">SUM(E4:J4)</f>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M4" s="6" t="n">
         <f aca="false">SUM(E4:K4)</f>
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>24</v>
-      </c>
       <c r="E5" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>8</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" s="11" t="n">
         <f aca="false">SUM(E5:J5)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M5" s="11" t="n">
         <f aca="false">SUM(E5:K5)</f>
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="E6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6" s="6" t="n">
         <f aca="false">SUM(E6:J6)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M6" s="6" t="n">
         <f aca="false">SUM(E6:K6)</f>
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>30</v>
-      </c>
       <c r="E7" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>9</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" s="11" t="n">
         <f aca="false">SUM(E7:J7)</f>
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M7" s="11" t="n">
         <f aca="false">SUM(E7:K7)</f>
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H8" s="2" t="n">
+      <c r="E8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" s="6" t="n">
+      <c r="K8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" s="11" t="n">
         <f aca="false">SUM(E8:J8)</f>
-        <v>44</v>
-      </c>
-      <c r="M8" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="M8" s="11" t="n">
         <f aca="false">SUM(E8:K8)</f>
         <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="E9" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>9</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>8</v>
@@ -1134,11 +1315,11 @@
         <v>5</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L9" s="11" t="n">
         <f aca="false">SUM(E9:J9)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M9" s="11" t="n">
         <f aca="false">SUM(E9:K9)</f>
@@ -1147,96 +1328,96 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="E10" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L10" s="6" t="n">
         <f aca="false">SUM(E10:J10)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M10" s="6" t="n">
         <f aca="false">SUM(E10:K10)</f>
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="E11" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>8</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="11" t="n">
         <f aca="false">SUM(E11:J11)</f>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M11" s="11" t="n">
         <f aca="false">SUM(E11:K11)</f>
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>43</v>
@@ -1245,38 +1426,38 @@
         <v>44</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L12" s="6" t="n">
         <f aca="false">SUM(E12:J12)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M12" s="6" t="n">
         <f aca="false">SUM(E12:K12)</f>
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>45</v>
@@ -1288,25 +1469,25 @@
         <v>47</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>7</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13" s="11" t="n">
         <f aca="false">SUM(E13:J13)</f>
@@ -1314,316 +1495,316 @@
       </c>
       <c r="M13" s="11" t="n">
         <f aca="false">SUM(E13:K13)</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H14" s="2" t="n">
+      <c r="E14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J14" s="2" t="n">
+      <c r="F14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="L14" s="6" t="n">
+      <c r="G14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" s="11" t="n">
         <f aca="false">SUM(E14:J14)</f>
-        <v>41</v>
-      </c>
-      <c r="M14" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="M14" s="11" t="n">
         <f aca="false">SUM(E14:K14)</f>
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="A15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H15" s="7" t="n">
+      <c r="E15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="11" t="n">
+      <c r="K15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" s="6" t="n">
         <f aca="false">SUM(E15:J15)</f>
         <v>42</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="6" t="n">
         <f aca="false">SUM(E15:K15)</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <f aca="false">SUM(E16:J16)</f>
+        <v>42</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <f aca="false">SUM(E16:K16)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="5" t="s">
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <f aca="false">SUM(E16:J16)</f>
-        <v>38</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <f aca="false">SUM(E16:K16)</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="s">
+      <c r="D17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" s="11" t="n">
+      <c r="E17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" s="6" t="n">
         <f aca="false">SUM(E17:J17)</f>
-        <v>46</v>
-      </c>
-      <c r="M17" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="M17" s="6" t="n">
         <f aca="false">SUM(E17:K17)</f>
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="E18" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L18" s="6" t="n">
         <f aca="false">SUM(E18:J18)</f>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M18" s="6" t="n">
         <f aca="false">SUM(E18:K18)</f>
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" s="11" t="n">
+      <c r="E19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" s="6" t="n">
         <f aca="false">SUM(E19:J19)</f>
         <v>42</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="6" t="n">
         <f aca="false">SUM(E19:K19)</f>
         <v>49</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="E20" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>9</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>9</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L20" s="6" t="n">
         <f aca="false">SUM(E20:J20)</f>
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M20" s="6" t="n">
         <f aca="false">SUM(E20:K20)</f>
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>67</v>
@@ -1632,10 +1813,10 @@
         <v>68</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>7</v>
@@ -1644,158 +1825,158 @@
         <v>6</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J21" s="7" t="n">
         <v>7</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L21" s="11" t="n">
         <f aca="false">SUM(E21:J21)</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M21" s="11" t="n">
         <f aca="false">SUM(E21:K21)</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <f aca="false">SUM(E22:J22)</f>
+        <v>41</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <f aca="false">SUM(E22:K22)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <f aca="false">SUM(E23:J23)</f>
+        <v>41</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <f aca="false">SUM(E23:K23)</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <f aca="false">SUM(E24:J24)</f>
+        <v>41</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <f aca="false">SUM(E24:K24)</f>
         <v>49</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <f aca="false">SUM(E22:J22)</f>
-        <v>40</v>
-      </c>
-      <c r="M22" s="6" t="n">
-        <f aca="false">SUM(E22:K22)</f>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="L23" s="11" t="n">
-        <f aca="false">SUM(E23:J23)</f>
-        <v>42</v>
-      </c>
-      <c r="M23" s="11" t="n">
-        <f aca="false">SUM(E23:K23)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <f aca="false">SUM(E24:J24)</f>
-        <v>42</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <f aca="false">SUM(E24:K24)</f>
-        <v>47</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>75</v>
@@ -1807,13 +1988,13 @@
         <v>7</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>8</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>7</v>
@@ -1822,11 +2003,11 @@
         <v>6</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L25" s="11" t="n">
         <f aca="false">SUM(E25:J25)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M25" s="11" t="n">
         <f aca="false">SUM(E25:K25)</f>
@@ -1834,50 +2015,504 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" s="11" t="n">
+        <f aca="false">SUM(E26:J26)</f>
+        <v>38</v>
+      </c>
+      <c r="M26" s="11" t="n">
+        <f aca="false">SUM(E26:K26)</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+    </row>
+    <row r="28" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <f aca="false">SUM(E28:J28)</f>
+        <v>46</v>
+      </c>
+      <c r="M28" s="17" t="n">
+        <f aca="false">SUM(E28:K28)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="22" t="n">
+        <f aca="false">SUM(E29:J29)</f>
+        <v>49</v>
+      </c>
+      <c r="M29" s="22" t="n">
+        <f aca="false">SUM(E29:K29)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <f aca="false">SUM(E30:J30)</f>
+        <v>47</v>
+      </c>
+      <c r="M30" s="17" t="n">
+        <f aca="false">SUM(E30:K30)</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L31" s="22" t="n">
+        <f aca="false">SUM(E31:J31)</f>
+        <v>44</v>
+      </c>
+      <c r="M31" s="22" t="n">
+        <f aca="false">SUM(E31:K31)</f>
         <v>51</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="2" t="n">
+    </row>
+    <row r="32" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H32" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J26" s="2" t="n">
+      <c r="I32" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" s="17" t="n">
+        <f aca="false">SUM(E32:J32)</f>
+        <v>45</v>
+      </c>
+      <c r="M32" s="17" t="n">
+        <f aca="false">SUM(E32:K32)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I33" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="22" t="n">
+        <f aca="false">SUM(E33:J33)</f>
+        <v>49</v>
+      </c>
+      <c r="M33" s="22" t="n">
+        <f aca="false">SUM(E33:K33)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <f aca="false">SUM(E26:J26)</f>
-        <v>41</v>
-      </c>
-      <c r="M26" s="6" t="n">
-        <f aca="false">SUM(E26:K26)</f>
-        <v>49</v>
+      <c r="H34" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L34" s="17" t="n">
+        <f aca="false">SUM(E34:J34)</f>
+        <v>45</v>
+      </c>
+      <c r="M34" s="17" t="n">
+        <f aca="false">SUM(E34:K34)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="K35" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="22" t="n">
+        <f aca="false">SUM(E35:J35)</f>
+        <v>44</v>
+      </c>
+      <c r="M35" s="22" t="n">
+        <f aca="false">SUM(E35:K35)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L36" s="17" t="n">
+        <f aca="false">SUM(E36:J36)</f>
+        <v>43</v>
+      </c>
+      <c r="M36" s="17" t="n">
+        <f aca="false">SUM(E36:K36)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K37" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="L37" s="22" t="n">
+        <f aca="false">SUM(E37:J37)</f>
+        <v>47</v>
+      </c>
+      <c r="M37" s="22" t="n">
+        <f aca="false">SUM(E37:K37)</f>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M26"/>
+  <autoFilter ref="A1:M37">
+    <sortState ref="A2:M37">
+      <sortCondition ref="A2:A37" descending="1" customList=""/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="A27:M27"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
